--- a/exports/NAM-INDIA_full_report.xlsx
+++ b/exports/NAM-INDIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.01</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.38541666666</v>
+        <v>44579.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>363.65</v>
+        <v>354</v>
       </c>
       <c r="I2" t="n">
         <v>356.202508275</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>0.32</v>
+        <v>-2.34</v>
       </c>
       <c r="L2" t="n">
-        <v>1.94</v>
+        <v>2.61</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>6.51</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>306.45</v>
+        <v>312.8</v>
       </c>
       <c r="I3" t="n">
         <v>310.6111250321019</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50</v>
+        <v>50.83333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>13.43</v>
+        <v>11.64</v>
       </c>
       <c r="L3" t="n">
         <v>3.32</v>
       </c>
       <c r="M3" t="n">
-        <v>1.46</v>
+        <v>2.46</v>
       </c>
       <c r="N3" t="n">
         <v>4.16</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.34</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44659.55208333334</v>
+        <v>44662.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>335.15</v>
+        <v>332.7</v>
       </c>
       <c r="I4" t="n">
         <v>333.9575305079404</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>7.15</v>
+        <v>6.36</v>
       </c>
       <c r="L4" t="n">
         <v>1.73</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.85</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44713.55208333334</v>
+        <v>44714.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>283.25</v>
+        <v>286.2</v>
       </c>
       <c r="I5" t="n">
         <v>285.7872572865944</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K5" t="n">
-        <v>14.86</v>
+        <v>13.98</v>
       </c>
       <c r="L5" t="n">
         <v>1.37</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44732.38541666666</v>
+        <v>44732.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>271</v>
+        <v>269.5</v>
       </c>
       <c r="I6" t="n">
         <v>270.1434284605297</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.31</v>
+        <v>-5.84</v>
       </c>
       <c r="L6" t="n">
-        <v>5.47</v>
+        <v>7.01</v>
       </c>
       <c r="M6" t="n">
         <v>2.55</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>7.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>282.15</v>
+        <v>288.3</v>
       </c>
       <c r="I7" t="n">
         <v>284.2269358219201</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.69</v>
+        <v>-6.98</v>
       </c>
       <c r="L7" t="n">
-        <v>5.57</v>
+        <v>7.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.93</v>
+        <v>1.51</v>
       </c>
       <c r="N7" t="n">
         <v>4.53</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.23</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44756.55208333334</v>
+        <v>44757.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>286.2</v>
+        <v>276</v>
       </c>
       <c r="I8" t="n">
         <v>280.3572725831574</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.73</v>
+        <v>-4.27</v>
       </c>
       <c r="L8" t="n">
         <v>7.54</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44776.38541666666</v>
+        <v>44776.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>288.15</v>
+        <v>300</v>
       </c>
       <c r="I9" t="n">
         <v>293.3964184931688</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>6.49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>0.92</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.41</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44806.38541666666</v>
+        <v>44806.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>299.3</v>
+        <v>292.65</v>
       </c>
       <c r="I10" t="n">
         <v>295.4553148249197</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.23</v>
+        <v>-2.45</v>
       </c>
       <c r="L10" t="n">
         <v>4.18</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.58</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44893.38541666666</v>
+        <v>44893.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>262.65</v>
+        <v>269.6</v>
       </c>
       <c r="I11" t="n">
         <v>266.6434089417169</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>86.83333333333333</v>
+        <v>87</v>
       </c>
       <c r="K11" t="n">
-        <v>10.25</v>
+        <v>7.88</v>
       </c>
       <c r="L11" t="n">
         <v>3.52</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.45</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>263</v>
+        <v>256.5</v>
       </c>
       <c r="I12" t="n">
         <v>260.8665131796014</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.45</v>
+        <v>-4.86</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>5.36</v>
       </c>
       <c r="M12" t="n">
         <v>0.09</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>5.25</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>235</v>
+        <v>247.05</v>
       </c>
       <c r="I13" t="n">
         <v>244.7693467513303</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>40</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>8.380000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="L13" t="n">
         <v>2.53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.52</v>
+        <v>5.53</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="O13" t="n">
         <v>-2.99</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>4.98</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44959.55208333334</v>
+        <v>44960.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>235</v>
+        <v>229.35</v>
       </c>
       <c r="I14" t="n">
         <v>234.7525879238027</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.88</v>
+        <v>-7.16</v>
       </c>
       <c r="L14" t="n">
-        <v>5.53</v>
+        <v>7.45</v>
       </c>
       <c r="M14" t="n">
         <v>0.04</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>224.5</v>
+        <v>227.7</v>
       </c>
       <c r="I15" t="n">
         <v>225.0104723756592</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>2.11</v>
+        <v>0.72</v>
       </c>
       <c r="L15" t="n">
         <v>3.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="N15" t="n">
         <v>2.45</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.39</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>220.5</v>
+        <v>217.3</v>
       </c>
       <c r="I16" t="n">
         <v>217.6929885017272</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.16</v>
+        <v>-4.57</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8</v>
+        <v>5.07</v>
       </c>
       <c r="M16" t="n">
         <v>0.99</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.12</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>210.4</v>
+        <v>214</v>
       </c>
       <c r="I17" t="n">
         <v>211.1674078506701</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>3.18</v>
+        <v>1.52</v>
       </c>
       <c r="L17" t="n">
         <v>2.16</v>
@@ -1410,7 +1613,7 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.04</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
         <v>-1.59</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.86</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45085.55208333334</v>
+        <v>45086.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>250</v>
+        <v>245.05</v>
       </c>
       <c r="I18" t="n">
         <v>246.4818626123842</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K18" t="n">
-        <v>16.82</v>
+        <v>14.51</v>
       </c>
       <c r="L18" t="n">
         <v>1.75</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>5.88</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45097.55208333334</v>
+        <v>45098.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>251.5</v>
+        <v>255.15</v>
       </c>
       <c r="I19" t="n">
         <v>252.4283697358838</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.63</v>
+        <v>-4.12</v>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>4.63</v>
       </c>
       <c r="M19" t="n">
-        <v>0.85</v>
+        <v>1.39</v>
       </c>
       <c r="N19" t="n">
         <v>2.36</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.56</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>367.6</v>
+        <v>355.65</v>
       </c>
       <c r="I20" t="n">
         <v>360.7442126132715</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>121.1666666666667</v>
+        <v>124</v>
       </c>
       <c r="K20" t="n">
-        <v>44.07</v>
+        <v>39.39</v>
       </c>
       <c r="L20" t="n">
         <v>2.49</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>11.89</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45229.55208333334</v>
+        <v>45230.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>370.25</v>
+        <v>384</v>
       </c>
       <c r="I21" t="n">
         <v>382.9993362676855</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.11</v>
+        <v>-7.97</v>
       </c>
       <c r="L21" t="n">
-        <v>6.42</v>
+        <v>9.34</v>
       </c>
       <c r="M21" t="n">
-        <v>0.65</v>
+        <v>1.46</v>
       </c>
       <c r="N21" t="n">
-        <v>3.64</v>
+        <v>5.6</v>
       </c>
       <c r="O21" t="n">
         <v>-2.56</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.56</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>438.7</v>
+        <v>435.05</v>
       </c>
       <c r="I22" t="n">
         <v>437.5293827535471</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K22" t="n">
-        <v>14.24</v>
+        <v>13.29</v>
       </c>
       <c r="L22" t="n">
         <v>3.05</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.16</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>467</v>
+        <v>468.7</v>
       </c>
       <c r="I23" t="n">
         <v>467.9694914231782</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.34</v>
+        <v>-7.73</v>
       </c>
       <c r="L23" t="n">
-        <v>8.42</v>
+        <v>8.91</v>
       </c>
       <c r="M23" t="n">
         <v>0.47</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.52</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45330.55208333334</v>
+        <v>45331.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>494</v>
+        <v>482.85</v>
       </c>
       <c r="I24" t="n">
         <v>485.8840867521041</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K24" t="n">
-        <v>5.4</v>
+        <v>3.02</v>
       </c>
       <c r="L24" t="n">
         <v>2.14</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>11</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45338.55208333334</v>
+        <v>45341.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>495.1</v>
+        <v>518.5</v>
       </c>
       <c r="I25" t="n">
         <v>514.5664393819209</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.54</v>
+        <v>-7.38</v>
       </c>
       <c r="L25" t="n">
-        <v>3.97</v>
+        <v>7.57</v>
       </c>
       <c r="M25" t="n">
         <v>1.39</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>3.27</v>
       </c>
       <c r="O25" t="n">
         <v>-2.02</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>9.49</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>503</v>
+        <v>488.75</v>
       </c>
       <c r="I26" t="n">
         <v>494.6083110537015</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.99</v>
+        <v>-5.74</v>
       </c>
       <c r="L26" t="n">
-        <v>5.46</v>
+        <v>6.13</v>
       </c>
       <c r="M26" t="n">
         <v>0.1</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.98</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>483.45</v>
+        <v>502.75</v>
       </c>
       <c r="I27" t="n">
         <v>488.075263386837</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>1.08</v>
+        <v>-2.86</v>
       </c>
       <c r="L27" t="n">
         <v>5.04</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.89</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>622.5</v>
+        <v>550</v>
       </c>
       <c r="I28" t="n">
         <v>585.6613734079775</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K28" t="n">
-        <v>23.82</v>
+        <v>9.4</v>
       </c>
       <c r="L28" t="n">
         <v>4.8</v>
@@ -2037,7 +2372,7 @@
         <v>3.31</v>
       </c>
       <c r="N28" t="n">
-        <v>3.03</v>
+        <v>11.65</v>
       </c>
       <c r="O28" t="n">
         <v>3.94</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>17.06</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>611</v>
+        <v>629.65</v>
       </c>
       <c r="I29" t="n">
         <v>620.9252087855846</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.09</v>
+        <v>-14.48</v>
       </c>
       <c r="L29" t="n">
-        <v>14.36</v>
+        <v>15.26</v>
       </c>
       <c r="M29" t="n">
         <v>2.71</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>11.75</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>638</v>
+        <v>621.75</v>
       </c>
       <c r="I30" t="n">
         <v>633.4075160582504</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>1.33</v>
+        <v>-1.25</v>
       </c>
       <c r="L30" t="n">
-        <v>3.04</v>
+        <v>7.95</v>
       </c>
       <c r="M30" t="n">
         <v>1.36</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.99</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>638.1</v>
+        <v>663.45</v>
       </c>
       <c r="I31" t="n">
         <v>658.5158282225973</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.63</v>
+        <v>-6.71</v>
       </c>
       <c r="L31" t="n">
         <v>8.300000000000001</v>
@@ -2208,7 +2579,7 @@
         <v>3.23</v>
       </c>
       <c r="N31" t="n">
-        <v>5.48</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="O31" t="n">
         <v>-2.04</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>689.5</v>
+        <v>665</v>
       </c>
       <c r="I32" t="n">
         <v>668.8538927440143</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K32" t="n">
-        <v>3.93</v>
+        <v>0.23</v>
       </c>
       <c r="L32" t="n">
         <v>2.65</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45576.38541666666</v>
+        <v>45576.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>669.7</v>
+        <v>700</v>
       </c>
       <c r="I33" t="n">
         <v>688.0084030035928</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.71</v>
+        <v>-5.26</v>
       </c>
       <c r="L33" t="n">
-        <v>4.96</v>
+        <v>6.53</v>
       </c>
       <c r="M33" t="n">
         <v>1.73</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.26</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45609.38541666666</v>
+        <v>45609.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>682.6</v>
+        <v>665.05</v>
       </c>
       <c r="I34" t="n">
         <v>681.9255474617387</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.49</v>
+        <v>-4.99</v>
       </c>
       <c r="L34" t="n">
         <v>6.43</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45632.55208333334</v>
+        <v>45635.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>716.9</v>
+        <v>735.65</v>
       </c>
       <c r="I35" t="n">
         <v>719.8400378288741</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.8</v>
+        <v>-10.62</v>
       </c>
       <c r="L35" t="n">
-        <v>8.859999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="M35" t="n">
         <v>2.64</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.27</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45652.55208333334</v>
+        <v>45653.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>742.7</v>
+        <v>734.5</v>
       </c>
       <c r="I36" t="n">
         <v>737.9629901338959</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K36" t="n">
-        <v>0.96</v>
+        <v>-0.16</v>
       </c>
       <c r="L36" t="n">
         <v>3.94</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>661.05</v>
+        <v>689.4</v>
       </c>
       <c r="I37" t="n">
         <v>688.6546639757851</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>10</v>
+        <v>6.14</v>
       </c>
       <c r="L37" t="n">
         <v>4.96</v>
@@ -2550,7 +2993,7 @@
         <v>1.1</v>
       </c>
       <c r="N37" t="n">
-        <v>3.78</v>
+        <v>3.93</v>
       </c>
       <c r="O37" t="n">
         <v>-1.82</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>10.92</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45680.55208333334</v>
+        <v>45681.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>653.35</v>
+        <v>620.4</v>
       </c>
       <c r="I38" t="n">
         <v>637.9705683458562</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.23</v>
+        <v>-10.01</v>
       </c>
       <c r="L38" t="n">
-        <v>8.15</v>
+        <v>10.64</v>
       </c>
       <c r="M38" t="n">
-        <v>0.31</v>
+        <v>2.04</v>
       </c>
       <c r="N38" t="n">
-        <v>3.43</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
         <v>3.93</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>11.74</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45693.38541666666</v>
+        <v>45693.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>625.1</v>
+        <v>631</v>
       </c>
       <c r="I39" t="n">
         <v>625.1606388653059</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.76</v>
+        <v>-1.71</v>
       </c>
       <c r="L39" t="n">
         <v>4.77</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.84</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>580</v>
+        <v>540.9</v>
       </c>
       <c r="I40" t="n">
         <v>568.8888073404728</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.08</v>
+        <v>-14.28</v>
       </c>
       <c r="L40" t="n">
-        <v>9.289999999999999</v>
+        <v>14.36</v>
       </c>
       <c r="M40" t="n">
-        <v>0.16</v>
+        <v>1.03</v>
       </c>
       <c r="N40" t="n">
-        <v>3.8</v>
+        <v>6.98</v>
       </c>
       <c r="O40" t="n">
         <v>8.23</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>14.87</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>543.65</v>
+        <v>563.85</v>
       </c>
       <c r="I41" t="n">
         <v>559.4609061024582</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.51</v>
+        <v>-4.24</v>
       </c>
       <c r="L41" t="n">
         <v>6.51</v>
@@ -2778,7 +3269,7 @@
         <v>0.9</v>
       </c>
       <c r="N41" t="n">
-        <v>3.42</v>
+        <v>3.64</v>
       </c>
       <c r="O41" t="n">
         <v>-6.98</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>9.09</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>563</v>
+        <v>532.35</v>
       </c>
       <c r="I42" t="n">
         <v>549.276775908129</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.15</v>
+        <v>-5.59</v>
       </c>
       <c r="L42" t="n">
-        <v>3.52</v>
+        <v>11.67</v>
       </c>
       <c r="M42" t="n">
-        <v>1.18</v>
+        <v>11.54</v>
       </c>
       <c r="N42" t="n">
-        <v>3.6</v>
+        <v>4.26</v>
       </c>
       <c r="O42" t="n">
         <v>3.64</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.07</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>550.35</v>
+        <v>580.2</v>
       </c>
       <c r="I43" t="n">
         <v>575.3231150648279</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.38</v>
+        <v>-8.99</v>
       </c>
       <c r="L43" t="n">
-        <v>6.83</v>
+        <v>9.35</v>
       </c>
       <c r="M43" t="n">
         <v>4.01</v>
       </c>
       <c r="N43" t="n">
-        <v>5.03</v>
+        <v>5.75</v>
       </c>
       <c r="O43" t="n">
         <v>-4.26</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>12.92</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45819.38541666666</v>
+        <v>45819.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>768.85</v>
+        <v>752.9</v>
       </c>
       <c r="I44" t="n">
         <v>753.4937801802394</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>32.51</v>
+        <v>29.77</v>
       </c>
       <c r="L44" t="n">
         <v>4.02</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45832.38541666666</v>
+        <v>45832.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>779.45</v>
+        <v>783</v>
       </c>
       <c r="I45" t="n">
         <v>780.1420562977091</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.53</v>
+        <v>-4</v>
       </c>
       <c r="L45" t="n">
         <v>4.46</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.76</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45866.38541666666</v>
+        <v>45866.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>812.1</v>
+        <v>790.5</v>
       </c>
       <c r="I46" t="n">
         <v>811.8183687576192</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K46" t="n">
-        <v>3.72</v>
+        <v>0.96</v>
       </c>
       <c r="L46" t="n">
         <v>1.39</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>830.1</v>
+        <v>851.35</v>
       </c>
       <c r="I47" t="n">
         <v>839.8771879804696</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.01</v>
+        <v>-7.7</v>
       </c>
       <c r="L47" t="n">
-        <v>5.63</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>1.17</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.7</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>819.4</v>
+        <v>812.65</v>
       </c>
       <c r="I48" t="n">
         <v>817.5994591008555</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.75</v>
+        <v>-4.55</v>
       </c>
       <c r="L48" t="n">
-        <v>4.49</v>
+        <v>5.06</v>
       </c>
       <c r="M48" t="n">
         <v>0.84</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.12</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45917.38541666666</v>
+        <v>45917.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>842.25</v>
+        <v>844</v>
       </c>
       <c r="I49" t="n">
         <v>842.6819770911185</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.64</v>
+        <v>-3.86</v>
       </c>
       <c r="L49" t="n">
-        <v>4.21</v>
+        <v>5.4</v>
       </c>
       <c r="M49" t="n">
         <v>0.98</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>4.31</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>910</v>
+        <v>859.6</v>
       </c>
       <c r="I50" t="n">
         <v>896.4325437081379</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K50" t="n">
-        <v>7.82</v>
+        <v>1.85</v>
       </c>
       <c r="L50" t="n">
         <v>1.57</v>
       </c>
       <c r="M50" t="n">
-        <v>0.92</v>
+        <v>4.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2.65</v>
+        <v>5.49</v>
       </c>
       <c r="O50" t="n">
         <v>1.11</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46003.38541666666</v>
+        <v>46003.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>855.6</v>
+        <v>866</v>
       </c>
       <c r="I51" t="n">
         <v>857.5790582757638</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>0.47</v>
+        <v>-0.74</v>
       </c>
       <c r="L51" t="n">
         <v>4.33</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>6.14</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>865</v>
+        <v>852.25</v>
       </c>
       <c r="I52" t="n">
         <v>852.5845160911023</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.12</v>
+        <v>-1.59</v>
       </c>
       <c r="L52" t="n">
-        <v>1.36</v>
+        <v>2.31</v>
       </c>
       <c r="M52" t="n">
         <v>0.23</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.91</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46051.38541666666</v>
+        <v>46051.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>847.85</v>
+        <v>861</v>
       </c>
       <c r="I53" t="n">
         <v>859.473022860941</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>0.52</v>
+        <v>-1.03</v>
       </c>
       <c r="L53" t="n">
         <v>7.07</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>7.3</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>933</v>
+        <v>903.6</v>
       </c>
       <c r="I54" t="n">
         <v>917.115575305965</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>8.359999999999999</v>
+        <v>4.95</v>
       </c>
       <c r="L54" t="n">
         <v>2.21</v>
       </c>
       <c r="M54" t="n">
-        <v>1.03</v>
+        <v>3.43</v>
       </c>
       <c r="N54" t="n">
         <v>5.04</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>832.4</v>
+        <v>917.25</v>
       </c>
       <c r="I55" t="n">
         <v>878.2896976236924</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K55" t="n">
-        <v>7.88</v>
+        <v>-1.51</v>
       </c>
       <c r="L55" t="n">
         <v>2.46</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.1</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46218.55208333334</v>
+        <v>46219.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1190.2</v>
+        <v>1144.8</v>
       </c>
       <c r="I56" t="n">
         <v>1157.407695783322</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>98.16666666666667</v>
+        <v>99</v>
       </c>
       <c r="K56" t="n">
-        <v>29.76</v>
+        <v>24.81</v>
       </c>
       <c r="L56" t="n">
         <v>6.24</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46237.55208333334</v>
+        <v>46238.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1162.5</v>
+        <v>1190.7</v>
       </c>
       <c r="I57" t="n">
         <v>1175.183292470824</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.55</v>
+        <v>-4.01</v>
       </c>
       <c r="L57" t="n">
         <v>5.4</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.21</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1192.6</v>
+        <v>1179.5</v>
       </c>
       <c r="I58" t="n">
         <v>1188.121380089311</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K58" t="n">
-        <v>0.16</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L58" t="n">
         <v>2.99</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>78</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5909,7 +6624,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.6</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="6">
@@ -5919,7 +6634,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -5929,7 +6644,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>121.2</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
@@ -5939,7 +6654,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5949,7 +6664,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -5959,7 +6674,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.1</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="11">
@@ -5969,7 +6684,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -5979,7 +6694,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -5989,7 +6704,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66.7</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="14">
@@ -5999,7 +6714,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.92</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="15">
@@ -6009,7 +6724,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.54</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="16">
@@ -6019,7 +6734,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.21</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="17">
@@ -6029,7 +6744,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.07</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="18">
@@ -6039,7 +6754,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6049,7 +6764,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.62</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="20">
@@ -6059,7 +6774,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.21</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="21">
@@ -6069,7 +6784,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.36</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="22">
@@ -6079,7 +6794,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6089,7 +6804,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -6099,7 +6814,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25">
@@ -6109,7 +6824,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.01</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="26">
@@ -6119,7 +6834,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.99</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="27">
@@ -6139,7 +6854,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
